--- a/artfynd/A 15788-2026 artfynd.xlsx
+++ b/artfynd/A 15788-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131983267</v>
       </c>
       <c r="B2" t="n">
-        <v>58381</v>
+        <v>58383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>132060941</v>
       </c>
       <c r="B3" t="n">
-        <v>58105</v>
+        <v>58107</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>132060882</v>
       </c>
       <c r="B5" t="n">
-        <v>58669</v>
+        <v>58671</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 15788-2026 artfynd.xlsx
+++ b/artfynd/A 15788-2026 artfynd.xlsx
@@ -889,27 +889,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132060958</v>
+        <v>132060882</v>
       </c>
       <c r="B4" t="n">
-        <v>57242</v>
+        <v>58671</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100038</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -998,27 +998,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132060882</v>
+        <v>132060958</v>
       </c>
       <c r="B5" t="n">
-        <v>58671</v>
+        <v>57242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>100038</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>

--- a/artfynd/A 15788-2026 artfynd.xlsx
+++ b/artfynd/A 15788-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131983267</v>
       </c>
       <c r="B2" t="n">
-        <v>58383</v>
+        <v>58384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>132060941</v>
       </c>
       <c r="B3" t="n">
-        <v>58107</v>
+        <v>58108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,27 +889,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132060882</v>
+        <v>132060958</v>
       </c>
       <c r="B4" t="n">
-        <v>58671</v>
+        <v>57243</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>100038</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -998,27 +998,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132060958</v>
+        <v>132060882</v>
       </c>
       <c r="B5" t="n">
-        <v>57242</v>
+        <v>58672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100038</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
         <v>132060962</v>
       </c>
       <c r="B6" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15788-2026 artfynd.xlsx
+++ b/artfynd/A 15788-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131983267</v>
       </c>
       <c r="B2" t="n">
-        <v>58384</v>
+        <v>58388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>132060941</v>
       </c>
       <c r="B3" t="n">
-        <v>58108</v>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>132060958</v>
       </c>
       <c r="B4" t="n">
-        <v>57243</v>
+        <v>57247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>132060882</v>
       </c>
       <c r="B5" t="n">
-        <v>58672</v>
+        <v>58676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>132060962</v>
       </c>
       <c r="B6" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15788-2026 artfynd.xlsx
+++ b/artfynd/A 15788-2026 artfynd.xlsx
@@ -889,27 +889,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132060958</v>
+        <v>132060882</v>
       </c>
       <c r="B4" t="n">
-        <v>57247</v>
+        <v>58676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100038</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -998,27 +998,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132060882</v>
+        <v>132060958</v>
       </c>
       <c r="B5" t="n">
-        <v>58676</v>
+        <v>57247</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>100038</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>

--- a/artfynd/A 15788-2026 artfynd.xlsx
+++ b/artfynd/A 15788-2026 artfynd.xlsx
@@ -889,27 +889,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132060882</v>
+        <v>132060958</v>
       </c>
       <c r="B4" t="n">
-        <v>58676</v>
+        <v>57247</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>100038</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -998,27 +998,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132060958</v>
+        <v>132060882</v>
       </c>
       <c r="B5" t="n">
-        <v>57247</v>
+        <v>58676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100038</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>

--- a/artfynd/A 15788-2026 artfynd.xlsx
+++ b/artfynd/A 15788-2026 artfynd.xlsx
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz, Per Muhr</t>
+          <t>Per Muhr, Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 15788-2026 artfynd.xlsx
+++ b/artfynd/A 15788-2026 artfynd.xlsx
@@ -889,27 +889,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132060958</v>
+        <v>132060882</v>
       </c>
       <c r="B4" t="n">
-        <v>57247</v>
+        <v>58676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100038</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -991,34 +991,34 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz, Per Muhr</t>
+          <t>Per Muhr, Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132060882</v>
+        <v>132060958</v>
       </c>
       <c r="B5" t="n">
-        <v>58676</v>
+        <v>57247</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>100038</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Muhr, Petra Borgcrantz</t>
+          <t>Petra Borgcrantz, Per Muhr</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 15788-2026 artfynd.xlsx
+++ b/artfynd/A 15788-2026 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>132060941</v>
       </c>
       <c r="B3" t="n">
-        <v>58112</v>
+        <v>58113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,27 +889,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132060882</v>
+        <v>132060958</v>
       </c>
       <c r="B4" t="n">
-        <v>58676</v>
+        <v>57248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>100038</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -991,34 +991,34 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Muhr, Petra Borgcrantz</t>
+          <t>Petra Borgcrantz, Per Muhr</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132060958</v>
+        <v>132060882</v>
       </c>
       <c r="B5" t="n">
-        <v>57247</v>
+        <v>58677</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100038</v>
+        <v>103055</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsduva</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Columba oenas</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1110,7 +1110,7 @@
         <v>132060962</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 15788-2026 artfynd.xlsx
+++ b/artfynd/A 15788-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132060958</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132060962</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131983267</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132060941</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,8 +1238,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132060882</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>